--- a/storage/templates/Generales.xlsx
+++ b/storage/templates/Generales.xlsx
@@ -285,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -373,6 +373,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -703,7 +706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN1003"/>
+  <dimension ref="A1:AN1008"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="1" min="1" max="1"/>
@@ -3529,40 +3532,385 @@
       </c>
     </row>
     <row r="43" ht="25.05" customHeight="1">
-      <c r="C43" s="9">
-        <f>SUM(C7:C42)</f>
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>758</t>
+        </is>
+      </c>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>CEPILLO BUQUE S/PALO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>7.05633</v>
+      </c>
+      <c r="F43" s="13">
+        <f>C43*E43</f>
         <v/>
       </c>
-      <c r="E43" s="11" t="inlineStr">
+      <c r="G43" s="19" t="n"/>
+      <c r="H43" s="19" t="n"/>
+      <c r="I43" s="19" t="n"/>
+      <c r="J43" s="19" t="n"/>
+      <c r="K43" s="19" t="n"/>
+      <c r="L43" s="19" t="n"/>
+      <c r="M43" s="19" t="n"/>
+      <c r="N43" s="19" t="n"/>
+      <c r="O43" s="19" t="n"/>
+      <c r="P43" s="19" t="n"/>
+      <c r="Q43" s="19" t="n"/>
+      <c r="R43" s="19" t="n"/>
+      <c r="S43" s="19" t="n"/>
+      <c r="T43" s="19" t="n"/>
+      <c r="U43" s="19" t="n"/>
+      <c r="V43" s="19" t="n"/>
+      <c r="W43" s="19" t="n"/>
+      <c r="X43" s="19" t="n"/>
+      <c r="Y43" s="19" t="n"/>
+      <c r="Z43" s="19" t="n"/>
+      <c r="AA43" s="19" t="n"/>
+      <c r="AB43" s="19" t="n"/>
+      <c r="AC43" s="19" t="n"/>
+      <c r="AD43" s="19" t="n"/>
+      <c r="AE43" s="19" t="n"/>
+      <c r="AF43" s="19" t="n"/>
+      <c r="AG43" s="19" t="n"/>
+      <c r="AH43" s="19" t="n"/>
+      <c r="AI43" s="19" t="n"/>
+      <c r="AJ43" s="19" t="n"/>
+      <c r="AK43" s="19" t="n"/>
+      <c r="AL43" s="20">
+        <f>SUM(G43:AK43)</f>
+        <v/>
+      </c>
+      <c r="AM43" s="21">
+        <f>SUM(C43,AL43)</f>
+        <v/>
+      </c>
+      <c r="AN43" s="23">
+        <f>E43*AM43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="25.05" customHeight="1">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t>3768</t>
+        </is>
+      </c>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>HARAGANES PLASTICO 75 CM</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="F44" s="13">
+        <f>C44*E44</f>
+        <v/>
+      </c>
+      <c r="G44" s="19" t="n"/>
+      <c r="H44" s="19" t="n"/>
+      <c r="I44" s="19" t="n"/>
+      <c r="J44" s="19" t="n"/>
+      <c r="K44" s="19" t="n"/>
+      <c r="L44" s="19" t="n"/>
+      <c r="M44" s="19" t="n"/>
+      <c r="N44" s="19" t="n"/>
+      <c r="O44" s="19" t="n"/>
+      <c r="P44" s="19" t="n"/>
+      <c r="Q44" s="19" t="n"/>
+      <c r="R44" s="19" t="n"/>
+      <c r="S44" s="19" t="n"/>
+      <c r="T44" s="19" t="n"/>
+      <c r="U44" s="19" t="n"/>
+      <c r="V44" s="19" t="n"/>
+      <c r="W44" s="19" t="n"/>
+      <c r="X44" s="19" t="n"/>
+      <c r="Y44" s="19" t="n"/>
+      <c r="Z44" s="19" t="n"/>
+      <c r="AA44" s="19" t="n"/>
+      <c r="AB44" s="19" t="n"/>
+      <c r="AC44" s="19" t="n"/>
+      <c r="AD44" s="19" t="n"/>
+      <c r="AE44" s="19" t="n"/>
+      <c r="AF44" s="19" t="n"/>
+      <c r="AG44" s="19" t="n"/>
+      <c r="AH44" s="19" t="n"/>
+      <c r="AI44" s="19" t="n"/>
+      <c r="AJ44" s="19" t="n"/>
+      <c r="AK44" s="19" t="n"/>
+      <c r="AL44" s="20">
+        <f>SUM(G44:AK44)</f>
+        <v/>
+      </c>
+      <c r="AM44" s="21">
+        <f>SUM(C44,AL44)</f>
+        <v/>
+      </c>
+      <c r="AN44" s="23">
+        <f>E44*AM44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="25.05" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t>8191</t>
+        </is>
+      </c>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>SUMA INOX D7 75 CL</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>BOTE</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>4.16267</v>
+      </c>
+      <c r="F45" s="13">
+        <f>C45*E45</f>
+        <v/>
+      </c>
+      <c r="G45" s="19" t="n"/>
+      <c r="H45" s="19" t="n"/>
+      <c r="I45" s="19" t="n"/>
+      <c r="J45" s="19" t="n"/>
+      <c r="K45" s="19" t="n"/>
+      <c r="L45" s="19" t="n"/>
+      <c r="M45" s="19" t="n"/>
+      <c r="N45" s="19" t="n"/>
+      <c r="O45" s="19" t="n"/>
+      <c r="P45" s="19" t="n"/>
+      <c r="Q45" s="19" t="n"/>
+      <c r="R45" s="19" t="n"/>
+      <c r="S45" s="19" t="n"/>
+      <c r="T45" s="19" t="n"/>
+      <c r="U45" s="19" t="n"/>
+      <c r="V45" s="19" t="n"/>
+      <c r="W45" s="19" t="n"/>
+      <c r="X45" s="19" t="n"/>
+      <c r="Y45" s="19" t="n"/>
+      <c r="Z45" s="19" t="n"/>
+      <c r="AA45" s="19" t="n"/>
+      <c r="AB45" s="19" t="n"/>
+      <c r="AC45" s="19" t="n"/>
+      <c r="AD45" s="19" t="n"/>
+      <c r="AE45" s="19" t="n"/>
+      <c r="AF45" s="19" t="n"/>
+      <c r="AG45" s="19" t="n"/>
+      <c r="AH45" s="19" t="n"/>
+      <c r="AI45" s="19" t="n"/>
+      <c r="AJ45" s="19" t="n"/>
+      <c r="AK45" s="19" t="n"/>
+      <c r="AL45" s="20">
+        <f>SUM(G45:AK45)</f>
+        <v/>
+      </c>
+      <c r="AM45" s="21">
+        <f>SUM(C45,AL45)</f>
+        <v/>
+      </c>
+      <c r="AN45" s="23">
+        <f>E45*AM45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="25.05" customHeight="1">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t>28113</t>
+        </is>
+      </c>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>ENSALADERA COMPOSTABLE 75 CL</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="F46" s="13">
+        <f>C46*E46</f>
+        <v/>
+      </c>
+      <c r="G46" s="19" t="n"/>
+      <c r="H46" s="19" t="n"/>
+      <c r="I46" s="19" t="n"/>
+      <c r="J46" s="19" t="n"/>
+      <c r="K46" s="19" t="n"/>
+      <c r="L46" s="19" t="n"/>
+      <c r="M46" s="19" t="n"/>
+      <c r="N46" s="19" t="n"/>
+      <c r="O46" s="19" t="n"/>
+      <c r="P46" s="19" t="n"/>
+      <c r="Q46" s="19" t="n"/>
+      <c r="R46" s="19" t="n"/>
+      <c r="S46" s="19" t="n"/>
+      <c r="T46" s="19" t="n"/>
+      <c r="U46" s="19" t="n"/>
+      <c r="V46" s="19" t="n"/>
+      <c r="W46" s="19" t="n"/>
+      <c r="X46" s="19" t="n"/>
+      <c r="Y46" s="19" t="n"/>
+      <c r="Z46" s="19" t="n"/>
+      <c r="AA46" s="19" t="n"/>
+      <c r="AB46" s="19" t="n"/>
+      <c r="AC46" s="19" t="n"/>
+      <c r="AD46" s="19" t="n"/>
+      <c r="AE46" s="19" t="n"/>
+      <c r="AF46" s="19" t="n"/>
+      <c r="AG46" s="19" t="n"/>
+      <c r="AH46" s="19" t="n"/>
+      <c r="AI46" s="19" t="n"/>
+      <c r="AJ46" s="19" t="n"/>
+      <c r="AK46" s="19" t="n"/>
+      <c r="AL46" s="20">
+        <f>SUM(G46:AK46)</f>
+        <v/>
+      </c>
+      <c r="AM46" s="21">
+        <f>SUM(C46,AL46)</f>
+        <v/>
+      </c>
+      <c r="AN46" s="23">
+        <f>E46*AM46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="25.05" customHeight="1">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t>28114</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>TAPA P/ENSALADERA COMPOSTABLE 75 CL</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>UNIDAD</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.0842</v>
+      </c>
+      <c r="F47" s="13">
+        <f>C47*E47</f>
+        <v/>
+      </c>
+      <c r="G47" s="19" t="n"/>
+      <c r="H47" s="19" t="n"/>
+      <c r="I47" s="19" t="n"/>
+      <c r="J47" s="19" t="n"/>
+      <c r="K47" s="19" t="n"/>
+      <c r="L47" s="19" t="n"/>
+      <c r="M47" s="19" t="n"/>
+      <c r="N47" s="19" t="n"/>
+      <c r="O47" s="19" t="n"/>
+      <c r="P47" s="19" t="n"/>
+      <c r="Q47" s="19" t="n"/>
+      <c r="R47" s="19" t="n"/>
+      <c r="S47" s="19" t="n"/>
+      <c r="T47" s="19" t="n"/>
+      <c r="U47" s="19" t="n"/>
+      <c r="V47" s="19" t="n"/>
+      <c r="W47" s="19" t="n"/>
+      <c r="X47" s="19" t="n"/>
+      <c r="Y47" s="19" t="n"/>
+      <c r="Z47" s="19" t="n"/>
+      <c r="AA47" s="19" t="n"/>
+      <c r="AB47" s="19" t="n"/>
+      <c r="AC47" s="19" t="n"/>
+      <c r="AD47" s="19" t="n"/>
+      <c r="AE47" s="19" t="n"/>
+      <c r="AF47" s="19" t="n"/>
+      <c r="AG47" s="19" t="n"/>
+      <c r="AH47" s="19" t="n"/>
+      <c r="AI47" s="19" t="n"/>
+      <c r="AJ47" s="19" t="n"/>
+      <c r="AK47" s="19" t="n"/>
+      <c r="AL47" s="20">
+        <f>SUM(G47:AK47)</f>
+        <v/>
+      </c>
+      <c r="AM47" s="21">
+        <f>SUM(C47,AL47)</f>
+        <v/>
+      </c>
+      <c r="AN47" s="23">
+        <f>E47*AM47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="9">
+        <f>SUM(C7:C47)</f>
+        <v/>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F43" s="12">
-        <f>SUM(F7:F42)</f>
+      <c r="F48" s="12">
+        <f>SUM(F7:F47)</f>
         <v/>
       </c>
-      <c r="AM43" s="9">
-        <f>SUM(AM7:AM42)</f>
+      <c r="AM48" s="9">
+        <f>SUM(AM7:AM47)</f>
         <v/>
       </c>
-      <c r="AN43" s="24">
-        <f>SUM(AN7:AN42)</f>
+      <c r="AN48" s="24">
+        <f>SUM(AN7:AN47)</f>
         <v/>
       </c>
     </row>
-    <row r="44" ht="25.05" customHeight="1">
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="F45" s="4" t="n"/>
-    </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
+    <row r="49">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="F50" s="4" t="n"/>
+    </row>
     <row r="51"/>
     <row r="52"/>
     <row r="53"/>
@@ -3713,186 +4061,11 @@
     <row r="198"/>
     <row r="199"/>
     <row r="200" ht="25.05" customHeight="1"/>
-    <row r="201" ht="25.05" customHeight="1">
-      <c r="G201" s="4" t="n"/>
-      <c r="H201" s="4" t="n"/>
-      <c r="I201" s="4" t="n"/>
-      <c r="J201" s="4" t="n"/>
-      <c r="K201" s="4" t="n"/>
-      <c r="L201" s="4" t="n"/>
-      <c r="M201" s="4" t="n"/>
-      <c r="N201" s="4" t="n"/>
-      <c r="O201" s="4" t="n"/>
-      <c r="P201" s="4" t="n"/>
-      <c r="Q201" s="4" t="n"/>
-      <c r="R201" s="4" t="n"/>
-      <c r="S201" s="4" t="n"/>
-      <c r="T201" s="4" t="n"/>
-      <c r="U201" s="4" t="n"/>
-      <c r="V201" s="4" t="n"/>
-      <c r="W201" s="4" t="n"/>
-      <c r="X201" s="4" t="n"/>
-      <c r="Y201" s="4" t="n"/>
-      <c r="Z201" s="4" t="n"/>
-      <c r="AA201" s="4" t="n"/>
-      <c r="AB201" s="4" t="n"/>
-      <c r="AC201" s="4" t="n"/>
-      <c r="AD201" s="4" t="n"/>
-      <c r="AE201" s="4" t="n"/>
-      <c r="AF201" s="4" t="n"/>
-      <c r="AG201" s="4" t="n"/>
-      <c r="AH201" s="4" t="n"/>
-      <c r="AI201" s="4" t="n"/>
-      <c r="AJ201" s="4" t="n"/>
-      <c r="AK201" s="4" t="n"/>
-      <c r="AL201" s="4" t="n"/>
-      <c r="AM201" s="4" t="n"/>
-      <c r="AN201" s="4" t="n"/>
-    </row>
-    <row r="202" ht="25.05" customHeight="1">
-      <c r="G202" s="4" t="n"/>
-      <c r="H202" s="4" t="n"/>
-      <c r="I202" s="4" t="n"/>
-      <c r="J202" s="4" t="n"/>
-      <c r="K202" s="4" t="n"/>
-      <c r="L202" s="4" t="n"/>
-      <c r="M202" s="4" t="n"/>
-      <c r="N202" s="4" t="n"/>
-      <c r="O202" s="4" t="n"/>
-      <c r="P202" s="4" t="n"/>
-      <c r="Q202" s="4" t="n"/>
-      <c r="R202" s="4" t="n"/>
-      <c r="S202" s="4" t="n"/>
-      <c r="T202" s="4" t="n"/>
-      <c r="U202" s="4" t="n"/>
-      <c r="V202" s="4" t="n"/>
-      <c r="W202" s="4" t="n"/>
-      <c r="X202" s="4" t="n"/>
-      <c r="Y202" s="4" t="n"/>
-      <c r="Z202" s="4" t="n"/>
-      <c r="AA202" s="4" t="n"/>
-      <c r="AB202" s="4" t="n"/>
-      <c r="AC202" s="4" t="n"/>
-      <c r="AD202" s="4" t="n"/>
-      <c r="AE202" s="4" t="n"/>
-      <c r="AF202" s="4" t="n"/>
-      <c r="AG202" s="4" t="n"/>
-      <c r="AH202" s="4" t="n"/>
-      <c r="AI202" s="4" t="n"/>
-      <c r="AJ202" s="4" t="n"/>
-      <c r="AK202" s="4" t="n"/>
-      <c r="AL202" s="4" t="n"/>
-      <c r="AM202" s="4" t="n"/>
-      <c r="AN202" s="4" t="n"/>
-    </row>
-    <row r="203" ht="25.05" customHeight="1">
-      <c r="G203" s="4" t="n"/>
-      <c r="H203" s="4" t="n"/>
-      <c r="I203" s="4" t="n"/>
-      <c r="J203" s="4" t="n"/>
-      <c r="K203" s="4" t="n"/>
-      <c r="L203" s="4" t="n"/>
-      <c r="M203" s="4" t="n"/>
-      <c r="N203" s="4" t="n"/>
-      <c r="O203" s="4" t="n"/>
-      <c r="P203" s="4" t="n"/>
-      <c r="Q203" s="4" t="n"/>
-      <c r="R203" s="4" t="n"/>
-      <c r="S203" s="4" t="n"/>
-      <c r="T203" s="4" t="n"/>
-      <c r="U203" s="4" t="n"/>
-      <c r="V203" s="4" t="n"/>
-      <c r="W203" s="4" t="n"/>
-      <c r="X203" s="4" t="n"/>
-      <c r="Y203" s="4" t="n"/>
-      <c r="Z203" s="4" t="n"/>
-      <c r="AA203" s="4" t="n"/>
-      <c r="AB203" s="4" t="n"/>
-      <c r="AC203" s="4" t="n"/>
-      <c r="AD203" s="4" t="n"/>
-      <c r="AE203" s="4" t="n"/>
-      <c r="AF203" s="4" t="n"/>
-      <c r="AG203" s="4" t="n"/>
-      <c r="AH203" s="4" t="n"/>
-      <c r="AI203" s="4" t="n"/>
-      <c r="AJ203" s="4" t="n"/>
-      <c r="AK203" s="4" t="n"/>
-      <c r="AL203" s="4" t="n"/>
-      <c r="AM203" s="4" t="n"/>
-      <c r="AN203" s="4" t="n"/>
-    </row>
-    <row r="204" ht="25.05" customHeight="1">
-      <c r="G204" s="4" t="n"/>
-      <c r="H204" s="4" t="n"/>
-      <c r="I204" s="4" t="n"/>
-      <c r="J204" s="4" t="n"/>
-      <c r="K204" s="4" t="n"/>
-      <c r="L204" s="4" t="n"/>
-      <c r="M204" s="4" t="n"/>
-      <c r="N204" s="4" t="n"/>
-      <c r="O204" s="4" t="n"/>
-      <c r="P204" s="4" t="n"/>
-      <c r="Q204" s="4" t="n"/>
-      <c r="R204" s="4" t="n"/>
-      <c r="S204" s="4" t="n"/>
-      <c r="T204" s="4" t="n"/>
-      <c r="U204" s="4" t="n"/>
-      <c r="V204" s="4" t="n"/>
-      <c r="W204" s="4" t="n"/>
-      <c r="X204" s="4" t="n"/>
-      <c r="Y204" s="4" t="n"/>
-      <c r="Z204" s="4" t="n"/>
-      <c r="AA204" s="4" t="n"/>
-      <c r="AB204" s="4" t="n"/>
-      <c r="AC204" s="4" t="n"/>
-      <c r="AD204" s="4" t="n"/>
-      <c r="AE204" s="4" t="n"/>
-      <c r="AF204" s="4" t="n"/>
-      <c r="AG204" s="4" t="n"/>
-      <c r="AH204" s="4" t="n"/>
-      <c r="AI204" s="4" t="n"/>
-      <c r="AJ204" s="4" t="n"/>
-      <c r="AK204" s="4" t="n"/>
-      <c r="AL204" s="4" t="n"/>
-      <c r="AM204" s="4" t="n"/>
-      <c r="AN204" s="4" t="n"/>
-    </row>
-    <row r="205" ht="25.05" customHeight="1">
-      <c r="G205" s="4" t="n"/>
-      <c r="H205" s="4" t="n"/>
-      <c r="I205" s="4" t="n"/>
-      <c r="J205" s="4" t="n"/>
-      <c r="K205" s="4" t="n"/>
-      <c r="L205" s="4" t="n"/>
-      <c r="M205" s="4" t="n"/>
-      <c r="N205" s="4" t="n"/>
-      <c r="O205" s="4" t="n"/>
-      <c r="P205" s="4" t="n"/>
-      <c r="Q205" s="4" t="n"/>
-      <c r="R205" s="4" t="n"/>
-      <c r="S205" s="4" t="n"/>
-      <c r="T205" s="4" t="n"/>
-      <c r="U205" s="4" t="n"/>
-      <c r="V205" s="4" t="n"/>
-      <c r="W205" s="4" t="n"/>
-      <c r="X205" s="4" t="n"/>
-      <c r="Y205" s="4" t="n"/>
-      <c r="Z205" s="4" t="n"/>
-      <c r="AA205" s="4" t="n"/>
-      <c r="AB205" s="4" t="n"/>
-      <c r="AC205" s="4" t="n"/>
-      <c r="AD205" s="4" t="n"/>
-      <c r="AE205" s="4" t="n"/>
-      <c r="AF205" s="4" t="n"/>
-      <c r="AG205" s="4" t="n"/>
-      <c r="AH205" s="4" t="n"/>
-      <c r="AI205" s="4" t="n"/>
-      <c r="AJ205" s="4" t="n"/>
-      <c r="AK205" s="4" t="n"/>
-      <c r="AL205" s="4" t="n"/>
-      <c r="AM205" s="4" t="n"/>
-      <c r="AN205" s="4" t="n"/>
-    </row>
+    <row r="201" ht="25.05" customHeight="1"/>
+    <row r="202" ht="25.05" customHeight="1"/>
+    <row r="203" ht="25.05" customHeight="1"/>
+    <row r="204" ht="25.05" customHeight="1"/>
+    <row r="205" ht="25.05" customHeight="1"/>
     <row r="206" ht="25.05" customHeight="1">
       <c r="G206" s="4" t="n"/>
       <c r="H206" s="4" t="n"/>
@@ -32621,6 +32794,186 @@
       <c r="AM1003" s="4" t="n"/>
       <c r="AN1003" s="4" t="n"/>
     </row>
+    <row r="1004">
+      <c r="G1004" s="4" t="n"/>
+      <c r="H1004" s="4" t="n"/>
+      <c r="I1004" s="4" t="n"/>
+      <c r="J1004" s="4" t="n"/>
+      <c r="K1004" s="4" t="n"/>
+      <c r="L1004" s="4" t="n"/>
+      <c r="M1004" s="4" t="n"/>
+      <c r="N1004" s="4" t="n"/>
+      <c r="O1004" s="4" t="n"/>
+      <c r="P1004" s="4" t="n"/>
+      <c r="Q1004" s="4" t="n"/>
+      <c r="R1004" s="4" t="n"/>
+      <c r="S1004" s="4" t="n"/>
+      <c r="T1004" s="4" t="n"/>
+      <c r="U1004" s="4" t="n"/>
+      <c r="V1004" s="4" t="n"/>
+      <c r="W1004" s="4" t="n"/>
+      <c r="X1004" s="4" t="n"/>
+      <c r="Y1004" s="4" t="n"/>
+      <c r="Z1004" s="4" t="n"/>
+      <c r="AA1004" s="4" t="n"/>
+      <c r="AB1004" s="4" t="n"/>
+      <c r="AC1004" s="4" t="n"/>
+      <c r="AD1004" s="4" t="n"/>
+      <c r="AE1004" s="4" t="n"/>
+      <c r="AF1004" s="4" t="n"/>
+      <c r="AG1004" s="4" t="n"/>
+      <c r="AH1004" s="4" t="n"/>
+      <c r="AI1004" s="4" t="n"/>
+      <c r="AJ1004" s="4" t="n"/>
+      <c r="AK1004" s="4" t="n"/>
+      <c r="AL1004" s="4" t="n"/>
+      <c r="AM1004" s="4" t="n"/>
+      <c r="AN1004" s="4" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="G1005" s="4" t="n"/>
+      <c r="H1005" s="4" t="n"/>
+      <c r="I1005" s="4" t="n"/>
+      <c r="J1005" s="4" t="n"/>
+      <c r="K1005" s="4" t="n"/>
+      <c r="L1005" s="4" t="n"/>
+      <c r="M1005" s="4" t="n"/>
+      <c r="N1005" s="4" t="n"/>
+      <c r="O1005" s="4" t="n"/>
+      <c r="P1005" s="4" t="n"/>
+      <c r="Q1005" s="4" t="n"/>
+      <c r="R1005" s="4" t="n"/>
+      <c r="S1005" s="4" t="n"/>
+      <c r="T1005" s="4" t="n"/>
+      <c r="U1005" s="4" t="n"/>
+      <c r="V1005" s="4" t="n"/>
+      <c r="W1005" s="4" t="n"/>
+      <c r="X1005" s="4" t="n"/>
+      <c r="Y1005" s="4" t="n"/>
+      <c r="Z1005" s="4" t="n"/>
+      <c r="AA1005" s="4" t="n"/>
+      <c r="AB1005" s="4" t="n"/>
+      <c r="AC1005" s="4" t="n"/>
+      <c r="AD1005" s="4" t="n"/>
+      <c r="AE1005" s="4" t="n"/>
+      <c r="AF1005" s="4" t="n"/>
+      <c r="AG1005" s="4" t="n"/>
+      <c r="AH1005" s="4" t="n"/>
+      <c r="AI1005" s="4" t="n"/>
+      <c r="AJ1005" s="4" t="n"/>
+      <c r="AK1005" s="4" t="n"/>
+      <c r="AL1005" s="4" t="n"/>
+      <c r="AM1005" s="4" t="n"/>
+      <c r="AN1005" s="4" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="G1006" s="4" t="n"/>
+      <c r="H1006" s="4" t="n"/>
+      <c r="I1006" s="4" t="n"/>
+      <c r="J1006" s="4" t="n"/>
+      <c r="K1006" s="4" t="n"/>
+      <c r="L1006" s="4" t="n"/>
+      <c r="M1006" s="4" t="n"/>
+      <c r="N1006" s="4" t="n"/>
+      <c r="O1006" s="4" t="n"/>
+      <c r="P1006" s="4" t="n"/>
+      <c r="Q1006" s="4" t="n"/>
+      <c r="R1006" s="4" t="n"/>
+      <c r="S1006" s="4" t="n"/>
+      <c r="T1006" s="4" t="n"/>
+      <c r="U1006" s="4" t="n"/>
+      <c r="V1006" s="4" t="n"/>
+      <c r="W1006" s="4" t="n"/>
+      <c r="X1006" s="4" t="n"/>
+      <c r="Y1006" s="4" t="n"/>
+      <c r="Z1006" s="4" t="n"/>
+      <c r="AA1006" s="4" t="n"/>
+      <c r="AB1006" s="4" t="n"/>
+      <c r="AC1006" s="4" t="n"/>
+      <c r="AD1006" s="4" t="n"/>
+      <c r="AE1006" s="4" t="n"/>
+      <c r="AF1006" s="4" t="n"/>
+      <c r="AG1006" s="4" t="n"/>
+      <c r="AH1006" s="4" t="n"/>
+      <c r="AI1006" s="4" t="n"/>
+      <c r="AJ1006" s="4" t="n"/>
+      <c r="AK1006" s="4" t="n"/>
+      <c r="AL1006" s="4" t="n"/>
+      <c r="AM1006" s="4" t="n"/>
+      <c r="AN1006" s="4" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="G1007" s="4" t="n"/>
+      <c r="H1007" s="4" t="n"/>
+      <c r="I1007" s="4" t="n"/>
+      <c r="J1007" s="4" t="n"/>
+      <c r="K1007" s="4" t="n"/>
+      <c r="L1007" s="4" t="n"/>
+      <c r="M1007" s="4" t="n"/>
+      <c r="N1007" s="4" t="n"/>
+      <c r="O1007" s="4" t="n"/>
+      <c r="P1007" s="4" t="n"/>
+      <c r="Q1007" s="4" t="n"/>
+      <c r="R1007" s="4" t="n"/>
+      <c r="S1007" s="4" t="n"/>
+      <c r="T1007" s="4" t="n"/>
+      <c r="U1007" s="4" t="n"/>
+      <c r="V1007" s="4" t="n"/>
+      <c r="W1007" s="4" t="n"/>
+      <c r="X1007" s="4" t="n"/>
+      <c r="Y1007" s="4" t="n"/>
+      <c r="Z1007" s="4" t="n"/>
+      <c r="AA1007" s="4" t="n"/>
+      <c r="AB1007" s="4" t="n"/>
+      <c r="AC1007" s="4" t="n"/>
+      <c r="AD1007" s="4" t="n"/>
+      <c r="AE1007" s="4" t="n"/>
+      <c r="AF1007" s="4" t="n"/>
+      <c r="AG1007" s="4" t="n"/>
+      <c r="AH1007" s="4" t="n"/>
+      <c r="AI1007" s="4" t="n"/>
+      <c r="AJ1007" s="4" t="n"/>
+      <c r="AK1007" s="4" t="n"/>
+      <c r="AL1007" s="4" t="n"/>
+      <c r="AM1007" s="4" t="n"/>
+      <c r="AN1007" s="4" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="G1008" s="4" t="n"/>
+      <c r="H1008" s="4" t="n"/>
+      <c r="I1008" s="4" t="n"/>
+      <c r="J1008" s="4" t="n"/>
+      <c r="K1008" s="4" t="n"/>
+      <c r="L1008" s="4" t="n"/>
+      <c r="M1008" s="4" t="n"/>
+      <c r="N1008" s="4" t="n"/>
+      <c r="O1008" s="4" t="n"/>
+      <c r="P1008" s="4" t="n"/>
+      <c r="Q1008" s="4" t="n"/>
+      <c r="R1008" s="4" t="n"/>
+      <c r="S1008" s="4" t="n"/>
+      <c r="T1008" s="4" t="n"/>
+      <c r="U1008" s="4" t="n"/>
+      <c r="V1008" s="4" t="n"/>
+      <c r="W1008" s="4" t="n"/>
+      <c r="X1008" s="4" t="n"/>
+      <c r="Y1008" s="4" t="n"/>
+      <c r="Z1008" s="4" t="n"/>
+      <c r="AA1008" s="4" t="n"/>
+      <c r="AB1008" s="4" t="n"/>
+      <c r="AC1008" s="4" t="n"/>
+      <c r="AD1008" s="4" t="n"/>
+      <c r="AE1008" s="4" t="n"/>
+      <c r="AF1008" s="4" t="n"/>
+      <c r="AG1008" s="4" t="n"/>
+      <c r="AH1008" s="4" t="n"/>
+      <c r="AI1008" s="4" t="n"/>
+      <c r="AJ1008" s="4" t="n"/>
+      <c r="AK1008" s="4" t="n"/>
+      <c r="AL1008" s="4" t="n"/>
+      <c r="AM1008" s="4" t="n"/>
+      <c r="AN1008" s="4" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A6:F6"/>
   <mergeCells count="3">
